--- a/Result/profitability/3105.xlsx
+++ b/Result/profitability/3105.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.74</v>
       </c>
       <c r="M2" t="n">
-        <v>0.71375</v>
+        <v>0.93375</v>
       </c>
       <c r="N2" t="n">
-        <v>23.94</v>
+        <v>24.7725</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6799999999999999</v>
+        <v>1.07125</v>
       </c>
       <c r="N3" t="n">
-        <v>24.5875</v>
+        <v>25.5625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7975</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>24.74625</v>
+        <v>26.185</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.83</v>
       </c>
       <c r="M5" t="n">
-        <v>0.89625</v>
+        <v>1.3075</v>
       </c>
       <c r="N5" t="n">
-        <v>26.12625</v>
+        <v>27.34875</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>98.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05125</v>
+        <v>1.02375</v>
       </c>
       <c r="N6" t="n">
-        <v>26.71875</v>
+        <v>26.89125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8225</v>
+        <v>0.8062499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>27.58625</v>
+        <v>27.14125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>0.69875</v>
+        <v>0.8287499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>27.23875</v>
+        <v>27.47625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9318,6 +9318,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5257</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3773</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1485</v>
+      </c>
+      <c r="F71" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="G71" t="n">
+        <v>742</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>14.11%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>447</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1188</v>
+      </c>
+      <c r="K71" t="n">
+        <v>977</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.9087499999999999</v>
+      </c>
+      <c r="N71" t="n">
+        <v>23.80625</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.8253968253968254</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.07213363705391029</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-3.323232323232323</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>9.779999999999998</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0.5297941495124592</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
